--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -590,7 +590,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1">
-        <v>3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#CharacterStat" sheetId="14" r:id="rId1"/>
@@ -102,10 +102,6 @@
     <t>StatDetail_Def_Base</t>
   </si>
   <si>
-    <t>CharacterLevelExp</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>StatDetailID</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -134,6 +130,10 @@
   </si>
   <si>
     <t>StatDetail_BlockRate_Base</t>
+  </si>
+  <si>
+    <t>CharacterLevelExp</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -282,7 +282,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -313,6 +313,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -590,7 +593,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -624,13 +627,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" s="10"/>
     </row>
@@ -743,7 +746,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" s="1">
         <v>2.5</v>
@@ -754,7 +757,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="1">
         <v>0.1</v>
@@ -765,7 +768,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="1">
         <v>0.1</v>
@@ -779,7 +782,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J603"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="6"/>
@@ -802,8 +805,8 @@
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>16</v>
+      <c r="B1" s="12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -848,7 +851,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -861,7 +864,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -874,7 +877,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="1">
-        <v>2500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -882,7 +885,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>3250</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -890,7 +893,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="1">
-        <v>4100</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -898,7 +901,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="1">
-        <v>4950</v>
+        <v>10110</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -906,7 +909,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="1">
-        <v>5800</v>
+        <v>11900</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -914,7 +917,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="1">
-        <v>6650</v>
+        <v>13690</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -922,7 +925,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="1">
-        <v>7500</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -930,7 +933,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="1">
-        <v>8350</v>
+        <v>17270</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -938,7 +941,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="1">
-        <v>9200</v>
+        <v>19060</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -946,7 +949,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="1">
-        <v>10050</v>
+        <v>20850</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
@@ -954,7 +957,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="1">
-        <v>10900</v>
+        <v>22640</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
@@ -962,7 +965,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="1">
-        <v>11750</v>
+        <v>24430</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
@@ -970,7 +973,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="1">
-        <v>12600</v>
+        <v>26220</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
@@ -978,7 +981,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="1">
-        <v>13450</v>
+        <v>28010</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
@@ -986,7 +989,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="1">
-        <v>14300</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
@@ -994,7 +997,7 @@
         <v>19</v>
       </c>
       <c r="C22" s="1">
-        <v>15150</v>
+        <v>31590</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
@@ -1002,7 +1005,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="1">
-        <v>16000</v>
+        <v>33380</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
@@ -1010,7 +1013,7 @@
         <v>21</v>
       </c>
       <c r="C24" s="1">
-        <v>16850</v>
+        <v>35170</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
@@ -1018,7 +1021,7 @@
         <v>22</v>
       </c>
       <c r="C25" s="1">
-        <v>17700</v>
+        <v>36960</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
@@ -1026,7 +1029,7 @@
         <v>23</v>
       </c>
       <c r="C26" s="1">
-        <v>18550</v>
+        <v>38750</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
@@ -1034,7 +1037,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="1">
-        <v>19400</v>
+        <v>40540</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
@@ -1042,7 +1045,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="1">
-        <v>20250</v>
+        <v>42330</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
@@ -1050,7 +1053,7 @@
         <v>26</v>
       </c>
       <c r="C29" s="1">
-        <v>21100</v>
+        <v>44120</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
@@ -1058,7 +1061,7 @@
         <v>27</v>
       </c>
       <c r="C30" s="1">
-        <v>21950</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
@@ -1066,7 +1069,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="1">
-        <v>22800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
@@ -1074,7 +1077,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="1">
-        <v>23650</v>
+        <v>49490</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
@@ -1082,7 +1085,7 @@
         <v>30</v>
       </c>
       <c r="C33" s="1">
-        <v>24500</v>
+        <v>51280</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
@@ -1090,7 +1093,7 @@
         <v>31</v>
       </c>
       <c r="C34" s="1">
-        <v>25350</v>
+        <v>53070</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
@@ -1098,7 +1101,7 @@
         <v>32</v>
       </c>
       <c r="C35" s="1">
-        <v>26200</v>
+        <v>54860</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
@@ -1106,7 +1109,7 @@
         <v>33</v>
       </c>
       <c r="C36" s="1">
-        <v>27050</v>
+        <v>56650</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
@@ -1114,7 +1117,7 @@
         <v>34</v>
       </c>
       <c r="C37" s="1">
-        <v>27900</v>
+        <v>58440</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
@@ -1122,7 +1125,7 @@
         <v>35</v>
       </c>
       <c r="C38" s="1">
-        <v>28750</v>
+        <v>60230</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
@@ -1130,7 +1133,7 @@
         <v>36</v>
       </c>
       <c r="C39" s="1">
-        <v>29600</v>
+        <v>62020</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
@@ -1138,7 +1141,7 @@
         <v>37</v>
       </c>
       <c r="C40" s="1">
-        <v>30450</v>
+        <v>63810</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
@@ -1146,7 +1149,7 @@
         <v>38</v>
       </c>
       <c r="C41" s="1">
-        <v>31300</v>
+        <v>65600</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
@@ -1154,7 +1157,7 @@
         <v>39</v>
       </c>
       <c r="C42" s="1">
-        <v>32150</v>
+        <v>67390</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
@@ -1162,7 +1165,7 @@
         <v>40</v>
       </c>
       <c r="C43" s="1">
-        <v>33000</v>
+        <v>69180</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.3">
@@ -1170,7 +1173,7 @@
         <v>41</v>
       </c>
       <c r="C44" s="1">
-        <v>33850</v>
+        <v>70970</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
@@ -1178,7 +1181,7 @@
         <v>42</v>
       </c>
       <c r="C45" s="1">
-        <v>34700</v>
+        <v>72760</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.3">
@@ -1186,7 +1189,7 @@
         <v>43</v>
       </c>
       <c r="C46" s="1">
-        <v>35550</v>
+        <v>74550</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
@@ -1194,7 +1197,7 @@
         <v>44</v>
       </c>
       <c r="C47" s="1">
-        <v>36400</v>
+        <v>76340</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.3">
@@ -1202,7 +1205,7 @@
         <v>45</v>
       </c>
       <c r="C48" s="1">
-        <v>37250</v>
+        <v>78130</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
@@ -1210,7 +1213,7 @@
         <v>46</v>
       </c>
       <c r="C49" s="1">
-        <v>38100</v>
+        <v>79920</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.3">
@@ -1218,7 +1221,7 @@
         <v>47</v>
       </c>
       <c r="C50" s="1">
-        <v>38950</v>
+        <v>81710</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
@@ -1226,7 +1229,7 @@
         <v>48</v>
       </c>
       <c r="C51" s="1">
-        <v>39800</v>
+        <v>83500</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
@@ -1234,7 +1237,7 @@
         <v>49</v>
       </c>
       <c r="C52" s="1">
-        <v>40650</v>
+        <v>85290</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
@@ -1242,7 +1245,7 @@
         <v>50</v>
       </c>
       <c r="C53" s="1">
-        <v>41500</v>
+        <v>87080</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.3">
@@ -1250,7 +1253,7 @@
         <v>51</v>
       </c>
       <c r="C54" s="1">
-        <v>42350</v>
+        <v>88870</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
@@ -1258,7 +1261,7 @@
         <v>52</v>
       </c>
       <c r="C55" s="1">
-        <v>43200</v>
+        <v>90660</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
@@ -1266,7 +1269,7 @@
         <v>53</v>
       </c>
       <c r="C56" s="1">
-        <v>44050</v>
+        <v>92450</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
@@ -1274,7 +1277,7 @@
         <v>54</v>
       </c>
       <c r="C57" s="1">
-        <v>44900</v>
+        <v>94240</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.3">
@@ -1282,7 +1285,7 @@
         <v>55</v>
       </c>
       <c r="C58" s="1">
-        <v>45750</v>
+        <v>96030</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
@@ -1290,7 +1293,7 @@
         <v>56</v>
       </c>
       <c r="C59" s="1">
-        <v>46600</v>
+        <v>97820</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.3">
@@ -1298,7 +1301,7 @@
         <v>57</v>
       </c>
       <c r="C60" s="1">
-        <v>47450</v>
+        <v>99610</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
@@ -1306,7 +1309,7 @@
         <v>58</v>
       </c>
       <c r="C61" s="1">
-        <v>48300</v>
+        <v>101400</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.3">
@@ -1314,7 +1317,7 @@
         <v>59</v>
       </c>
       <c r="C62" s="1">
-        <v>49150</v>
+        <v>103190</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
@@ -1322,7 +1325,7 @@
         <v>60</v>
       </c>
       <c r="C63" s="1">
-        <v>50000</v>
+        <v>104980</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.3">
@@ -1330,7 +1333,7 @@
         <v>61</v>
       </c>
       <c r="C64" s="1">
-        <v>50850</v>
+        <v>106770</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.3">
@@ -1338,7 +1341,7 @@
         <v>62</v>
       </c>
       <c r="C65" s="1">
-        <v>51700</v>
+        <v>108560</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.3">
@@ -1346,7 +1349,7 @@
         <v>63</v>
       </c>
       <c r="C66" s="1">
-        <v>52550</v>
+        <v>110350</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.3">
@@ -1354,7 +1357,7 @@
         <v>64</v>
       </c>
       <c r="C67" s="1">
-        <v>53400</v>
+        <v>112140</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.3">
@@ -1362,7 +1365,7 @@
         <v>65</v>
       </c>
       <c r="C68" s="1">
-        <v>54250</v>
+        <v>113930</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
@@ -1370,7 +1373,7 @@
         <v>66</v>
       </c>
       <c r="C69" s="1">
-        <v>55100</v>
+        <v>115720</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.3">
@@ -1378,7 +1381,7 @@
         <v>67</v>
       </c>
       <c r="C70" s="1">
-        <v>55950</v>
+        <v>117510</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.3">
@@ -1386,7 +1389,7 @@
         <v>68</v>
       </c>
       <c r="C71" s="1">
-        <v>56800</v>
+        <v>119300</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.3">
@@ -1394,7 +1397,7 @@
         <v>69</v>
       </c>
       <c r="C72" s="1">
-        <v>57650</v>
+        <v>121090</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.3">
@@ -1402,7 +1405,7 @@
         <v>70</v>
       </c>
       <c r="C73" s="1">
-        <v>58500</v>
+        <v>122880</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.3">
@@ -1410,7 +1413,7 @@
         <v>71</v>
       </c>
       <c r="C74" s="1">
-        <v>59350</v>
+        <v>124670</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.3">
@@ -1418,7 +1421,7 @@
         <v>72</v>
       </c>
       <c r="C75" s="1">
-        <v>60200</v>
+        <v>126460</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.3">
@@ -1426,7 +1429,7 @@
         <v>73</v>
       </c>
       <c r="C76" s="1">
-        <v>61050</v>
+        <v>128250</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.3">
@@ -1434,7 +1437,7 @@
         <v>74</v>
       </c>
       <c r="C77" s="1">
-        <v>61900</v>
+        <v>130040</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.3">
@@ -1442,7 +1445,7 @@
         <v>75</v>
       </c>
       <c r="C78" s="1">
-        <v>62750</v>
+        <v>131830</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.3">
@@ -1450,7 +1453,7 @@
         <v>76</v>
       </c>
       <c r="C79" s="1">
-        <v>63600</v>
+        <v>133620</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.3">
@@ -1458,7 +1461,7 @@
         <v>77</v>
       </c>
       <c r="C80" s="1">
-        <v>64450</v>
+        <v>135410</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
@@ -1466,7 +1469,7 @@
         <v>78</v>
       </c>
       <c r="C81" s="1">
-        <v>65300</v>
+        <v>137200</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
@@ -1474,7 +1477,7 @@
         <v>79</v>
       </c>
       <c r="C82" s="1">
-        <v>66150</v>
+        <v>138990</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
@@ -1482,7 +1485,7 @@
         <v>80</v>
       </c>
       <c r="C83" s="1">
-        <v>67000</v>
+        <v>140780</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.3">
@@ -1490,7 +1493,7 @@
         <v>81</v>
       </c>
       <c r="C84" s="1">
-        <v>67850</v>
+        <v>142570</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
@@ -1498,7 +1501,7 @@
         <v>82</v>
       </c>
       <c r="C85" s="1">
-        <v>68700</v>
+        <v>144360</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
@@ -1506,7 +1509,7 @@
         <v>83</v>
       </c>
       <c r="C86" s="1">
-        <v>69550</v>
+        <v>146150</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
@@ -1514,7 +1517,7 @@
         <v>84</v>
       </c>
       <c r="C87" s="1">
-        <v>70400</v>
+        <v>147940</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.3">
@@ -1522,7 +1525,7 @@
         <v>85</v>
       </c>
       <c r="C88" s="1">
-        <v>71250</v>
+        <v>149730</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
@@ -1530,7 +1533,7 @@
         <v>86</v>
       </c>
       <c r="C89" s="1">
-        <v>72100</v>
+        <v>151520</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.3">
@@ -1538,7 +1541,7 @@
         <v>87</v>
       </c>
       <c r="C90" s="1">
-        <v>72950</v>
+        <v>153310</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
@@ -1546,7 +1549,7 @@
         <v>88</v>
       </c>
       <c r="C91" s="1">
-        <v>73800</v>
+        <v>155100</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.3">
@@ -1554,7 +1557,7 @@
         <v>89</v>
       </c>
       <c r="C92" s="1">
-        <v>74650</v>
+        <v>156890</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
@@ -1562,7 +1565,7 @@
         <v>90</v>
       </c>
       <c r="C93" s="1">
-        <v>75500</v>
+        <v>158680</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.3">
@@ -1570,7 +1573,7 @@
         <v>91</v>
       </c>
       <c r="C94" s="1">
-        <v>76350</v>
+        <v>160470</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
@@ -1578,7 +1581,7 @@
         <v>92</v>
       </c>
       <c r="C95" s="1">
-        <v>77200</v>
+        <v>162260</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.3">
@@ -1586,7 +1589,7 @@
         <v>93</v>
       </c>
       <c r="C96" s="1">
-        <v>78050</v>
+        <v>164050</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
@@ -1594,7 +1597,7 @@
         <v>94</v>
       </c>
       <c r="C97" s="1">
-        <v>78900</v>
+        <v>165840</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.3">
@@ -1602,7 +1605,7 @@
         <v>95</v>
       </c>
       <c r="C98" s="1">
-        <v>79750</v>
+        <v>167630</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
@@ -1610,7 +1613,7 @@
         <v>96</v>
       </c>
       <c r="C99" s="1">
-        <v>80600</v>
+        <v>169420</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
@@ -1618,7 +1621,7 @@
         <v>97</v>
       </c>
       <c r="C100" s="1">
-        <v>81450</v>
+        <v>171210</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.3">
@@ -1626,7 +1629,7 @@
         <v>98</v>
       </c>
       <c r="C101" s="1">
-        <v>82300</v>
+        <v>173000</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
@@ -1634,7 +1637,7 @@
         <v>99</v>
       </c>
       <c r="C102" s="1">
-        <v>83150</v>
+        <v>174790</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.3">
@@ -1642,7 +1645,4007 @@
         <v>100</v>
       </c>
       <c r="C103" s="1">
-        <v>84000</v>
+        <v>176580</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B104" s="1">
+        <v>101</v>
+      </c>
+      <c r="C104" s="1">
+        <v>178370</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B105" s="1">
+        <v>102</v>
+      </c>
+      <c r="C105" s="1">
+        <v>180160</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B106" s="1">
+        <v>103</v>
+      </c>
+      <c r="C106" s="1">
+        <v>181950</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B107" s="1">
+        <v>104</v>
+      </c>
+      <c r="C107" s="1">
+        <v>183740</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B108" s="1">
+        <v>105</v>
+      </c>
+      <c r="C108" s="1">
+        <v>185530</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B109" s="1">
+        <v>106</v>
+      </c>
+      <c r="C109" s="1">
+        <v>187320</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B110" s="1">
+        <v>107</v>
+      </c>
+      <c r="C110" s="1">
+        <v>189110</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B111" s="1">
+        <v>108</v>
+      </c>
+      <c r="C111" s="1">
+        <v>190900</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B112" s="1">
+        <v>109</v>
+      </c>
+      <c r="C112" s="1">
+        <v>192690</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B113" s="1">
+        <v>110</v>
+      </c>
+      <c r="C113" s="1">
+        <v>194480</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B114" s="1">
+        <v>111</v>
+      </c>
+      <c r="C114" s="1">
+        <v>196270</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B115" s="1">
+        <v>112</v>
+      </c>
+      <c r="C115" s="1">
+        <v>198060</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B116" s="1">
+        <v>113</v>
+      </c>
+      <c r="C116" s="1">
+        <v>199850</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B117" s="1">
+        <v>114</v>
+      </c>
+      <c r="C117" s="1">
+        <v>201640</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B118" s="1">
+        <v>115</v>
+      </c>
+      <c r="C118" s="1">
+        <v>203430</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B119" s="1">
+        <v>116</v>
+      </c>
+      <c r="C119" s="1">
+        <v>205220</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B120" s="1">
+        <v>117</v>
+      </c>
+      <c r="C120" s="1">
+        <v>207010</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B121" s="1">
+        <v>118</v>
+      </c>
+      <c r="C121" s="1">
+        <v>208800</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B122" s="1">
+        <v>119</v>
+      </c>
+      <c r="C122" s="1">
+        <v>210590</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B123" s="1">
+        <v>120</v>
+      </c>
+      <c r="C123" s="1">
+        <v>212380</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B124" s="1">
+        <v>121</v>
+      </c>
+      <c r="C124" s="1">
+        <v>214170</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B125" s="1">
+        <v>122</v>
+      </c>
+      <c r="C125" s="1">
+        <v>215960</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B126" s="1">
+        <v>123</v>
+      </c>
+      <c r="C126" s="1">
+        <v>217750</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B127" s="1">
+        <v>124</v>
+      </c>
+      <c r="C127" s="1">
+        <v>219540</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B128" s="1">
+        <v>125</v>
+      </c>
+      <c r="C128" s="1">
+        <v>221330</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B129" s="1">
+        <v>126</v>
+      </c>
+      <c r="C129" s="1">
+        <v>223120</v>
+      </c>
+    </row>
+    <row r="130" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B130" s="1">
+        <v>127</v>
+      </c>
+      <c r="C130" s="1">
+        <v>224910</v>
+      </c>
+    </row>
+    <row r="131" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B131" s="1">
+        <v>128</v>
+      </c>
+      <c r="C131" s="1">
+        <v>226700</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B132" s="1">
+        <v>129</v>
+      </c>
+      <c r="C132" s="1">
+        <v>228490</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B133" s="1">
+        <v>130</v>
+      </c>
+      <c r="C133" s="1">
+        <v>230280</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B134" s="1">
+        <v>131</v>
+      </c>
+      <c r="C134" s="1">
+        <v>232070</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B135" s="1">
+        <v>132</v>
+      </c>
+      <c r="C135" s="1">
+        <v>233860</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B136" s="1">
+        <v>133</v>
+      </c>
+      <c r="C136" s="1">
+        <v>235650</v>
+      </c>
+    </row>
+    <row r="137" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B137" s="1">
+        <v>134</v>
+      </c>
+      <c r="C137" s="1">
+        <v>237440</v>
+      </c>
+    </row>
+    <row r="138" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B138" s="1">
+        <v>135</v>
+      </c>
+      <c r="C138" s="1">
+        <v>239230</v>
+      </c>
+    </row>
+    <row r="139" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B139" s="1">
+        <v>136</v>
+      </c>
+      <c r="C139" s="1">
+        <v>241020</v>
+      </c>
+    </row>
+    <row r="140" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B140" s="1">
+        <v>137</v>
+      </c>
+      <c r="C140" s="1">
+        <v>242810</v>
+      </c>
+    </row>
+    <row r="141" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B141" s="1">
+        <v>138</v>
+      </c>
+      <c r="C141" s="1">
+        <v>244600</v>
+      </c>
+    </row>
+    <row r="142" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B142" s="1">
+        <v>139</v>
+      </c>
+      <c r="C142" s="1">
+        <v>246390</v>
+      </c>
+    </row>
+    <row r="143" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B143" s="1">
+        <v>140</v>
+      </c>
+      <c r="C143" s="1">
+        <v>248180</v>
+      </c>
+    </row>
+    <row r="144" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B144" s="1">
+        <v>141</v>
+      </c>
+      <c r="C144" s="1">
+        <v>249970</v>
+      </c>
+    </row>
+    <row r="145" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B145" s="1">
+        <v>142</v>
+      </c>
+      <c r="C145" s="1">
+        <v>251760</v>
+      </c>
+    </row>
+    <row r="146" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B146" s="1">
+        <v>143</v>
+      </c>
+      <c r="C146" s="1">
+        <v>253550</v>
+      </c>
+    </row>
+    <row r="147" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B147" s="1">
+        <v>144</v>
+      </c>
+      <c r="C147" s="1">
+        <v>255340</v>
+      </c>
+    </row>
+    <row r="148" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B148" s="1">
+        <v>145</v>
+      </c>
+      <c r="C148" s="1">
+        <v>257130</v>
+      </c>
+    </row>
+    <row r="149" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B149" s="1">
+        <v>146</v>
+      </c>
+      <c r="C149" s="1">
+        <v>258920</v>
+      </c>
+    </row>
+    <row r="150" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B150" s="1">
+        <v>147</v>
+      </c>
+      <c r="C150" s="1">
+        <v>260710</v>
+      </c>
+    </row>
+    <row r="151" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B151" s="1">
+        <v>148</v>
+      </c>
+      <c r="C151" s="1">
+        <v>262500</v>
+      </c>
+    </row>
+    <row r="152" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B152" s="1">
+        <v>149</v>
+      </c>
+      <c r="C152" s="1">
+        <v>264290</v>
+      </c>
+    </row>
+    <row r="153" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B153" s="1">
+        <v>150</v>
+      </c>
+      <c r="C153" s="1">
+        <v>266080</v>
+      </c>
+    </row>
+    <row r="154" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B154" s="1">
+        <v>151</v>
+      </c>
+      <c r="C154" s="1">
+        <v>267870</v>
+      </c>
+    </row>
+    <row r="155" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B155" s="1">
+        <v>152</v>
+      </c>
+      <c r="C155" s="1">
+        <v>269660</v>
+      </c>
+    </row>
+    <row r="156" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B156" s="1">
+        <v>153</v>
+      </c>
+      <c r="C156" s="1">
+        <v>271450</v>
+      </c>
+    </row>
+    <row r="157" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B157" s="1">
+        <v>154</v>
+      </c>
+      <c r="C157" s="1">
+        <v>273240</v>
+      </c>
+    </row>
+    <row r="158" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B158" s="1">
+        <v>155</v>
+      </c>
+      <c r="C158" s="1">
+        <v>275030</v>
+      </c>
+    </row>
+    <row r="159" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B159" s="1">
+        <v>156</v>
+      </c>
+      <c r="C159" s="1">
+        <v>276820</v>
+      </c>
+    </row>
+    <row r="160" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B160" s="1">
+        <v>157</v>
+      </c>
+      <c r="C160" s="1">
+        <v>278610</v>
+      </c>
+    </row>
+    <row r="161" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B161" s="1">
+        <v>158</v>
+      </c>
+      <c r="C161" s="1">
+        <v>280400</v>
+      </c>
+    </row>
+    <row r="162" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B162" s="1">
+        <v>159</v>
+      </c>
+      <c r="C162" s="1">
+        <v>282190</v>
+      </c>
+    </row>
+    <row r="163" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B163" s="1">
+        <v>160</v>
+      </c>
+      <c r="C163" s="1">
+        <v>283980</v>
+      </c>
+    </row>
+    <row r="164" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B164" s="1">
+        <v>161</v>
+      </c>
+      <c r="C164" s="1">
+        <v>285770</v>
+      </c>
+    </row>
+    <row r="165" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B165" s="1">
+        <v>162</v>
+      </c>
+      <c r="C165" s="1">
+        <v>287560</v>
+      </c>
+    </row>
+    <row r="166" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B166" s="1">
+        <v>163</v>
+      </c>
+      <c r="C166" s="1">
+        <v>289350</v>
+      </c>
+    </row>
+    <row r="167" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B167" s="1">
+        <v>164</v>
+      </c>
+      <c r="C167" s="1">
+        <v>291140</v>
+      </c>
+    </row>
+    <row r="168" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B168" s="1">
+        <v>165</v>
+      </c>
+      <c r="C168" s="1">
+        <v>292930</v>
+      </c>
+    </row>
+    <row r="169" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B169" s="1">
+        <v>166</v>
+      </c>
+      <c r="C169" s="1">
+        <v>294720</v>
+      </c>
+    </row>
+    <row r="170" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B170" s="1">
+        <v>167</v>
+      </c>
+      <c r="C170" s="1">
+        <v>296510</v>
+      </c>
+    </row>
+    <row r="171" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B171" s="1">
+        <v>168</v>
+      </c>
+      <c r="C171" s="1">
+        <v>298300</v>
+      </c>
+    </row>
+    <row r="172" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B172" s="1">
+        <v>169</v>
+      </c>
+      <c r="C172" s="1">
+        <v>300090</v>
+      </c>
+    </row>
+    <row r="173" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B173" s="1">
+        <v>170</v>
+      </c>
+      <c r="C173" s="1">
+        <v>301880</v>
+      </c>
+    </row>
+    <row r="174" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B174" s="1">
+        <v>171</v>
+      </c>
+      <c r="C174" s="1">
+        <v>303670</v>
+      </c>
+    </row>
+    <row r="175" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B175" s="1">
+        <v>172</v>
+      </c>
+      <c r="C175" s="1">
+        <v>305460</v>
+      </c>
+    </row>
+    <row r="176" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B176" s="1">
+        <v>173</v>
+      </c>
+      <c r="C176" s="1">
+        <v>307250</v>
+      </c>
+    </row>
+    <row r="177" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B177" s="1">
+        <v>174</v>
+      </c>
+      <c r="C177" s="1">
+        <v>309040</v>
+      </c>
+    </row>
+    <row r="178" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B178" s="1">
+        <v>175</v>
+      </c>
+      <c r="C178" s="1">
+        <v>310830</v>
+      </c>
+    </row>
+    <row r="179" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B179" s="1">
+        <v>176</v>
+      </c>
+      <c r="C179" s="1">
+        <v>312620</v>
+      </c>
+    </row>
+    <row r="180" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B180" s="1">
+        <v>177</v>
+      </c>
+      <c r="C180" s="1">
+        <v>314410</v>
+      </c>
+    </row>
+    <row r="181" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B181" s="1">
+        <v>178</v>
+      </c>
+      <c r="C181" s="1">
+        <v>316200</v>
+      </c>
+    </row>
+    <row r="182" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B182" s="1">
+        <v>179</v>
+      </c>
+      <c r="C182" s="1">
+        <v>317990</v>
+      </c>
+    </row>
+    <row r="183" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B183" s="1">
+        <v>180</v>
+      </c>
+      <c r="C183" s="1">
+        <v>319780</v>
+      </c>
+    </row>
+    <row r="184" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B184" s="1">
+        <v>181</v>
+      </c>
+      <c r="C184" s="1">
+        <v>321570</v>
+      </c>
+    </row>
+    <row r="185" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B185" s="1">
+        <v>182</v>
+      </c>
+      <c r="C185" s="1">
+        <v>323360</v>
+      </c>
+    </row>
+    <row r="186" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B186" s="1">
+        <v>183</v>
+      </c>
+      <c r="C186" s="1">
+        <v>325150</v>
+      </c>
+    </row>
+    <row r="187" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B187" s="1">
+        <v>184</v>
+      </c>
+      <c r="C187" s="1">
+        <v>326940</v>
+      </c>
+    </row>
+    <row r="188" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B188" s="1">
+        <v>185</v>
+      </c>
+      <c r="C188" s="1">
+        <v>328730</v>
+      </c>
+    </row>
+    <row r="189" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B189" s="1">
+        <v>186</v>
+      </c>
+      <c r="C189" s="1">
+        <v>330520</v>
+      </c>
+    </row>
+    <row r="190" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B190" s="1">
+        <v>187</v>
+      </c>
+      <c r="C190" s="1">
+        <v>332310</v>
+      </c>
+    </row>
+    <row r="191" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B191" s="1">
+        <v>188</v>
+      </c>
+      <c r="C191" s="1">
+        <v>334100</v>
+      </c>
+    </row>
+    <row r="192" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B192" s="1">
+        <v>189</v>
+      </c>
+      <c r="C192" s="1">
+        <v>335890</v>
+      </c>
+    </row>
+    <row r="193" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B193" s="1">
+        <v>190</v>
+      </c>
+      <c r="C193" s="1">
+        <v>337680</v>
+      </c>
+    </row>
+    <row r="194" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B194" s="1">
+        <v>191</v>
+      </c>
+      <c r="C194" s="1">
+        <v>339470</v>
+      </c>
+    </row>
+    <row r="195" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B195" s="1">
+        <v>192</v>
+      </c>
+      <c r="C195" s="1">
+        <v>341260</v>
+      </c>
+    </row>
+    <row r="196" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B196" s="1">
+        <v>193</v>
+      </c>
+      <c r="C196" s="1">
+        <v>343050</v>
+      </c>
+    </row>
+    <row r="197" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B197" s="1">
+        <v>194</v>
+      </c>
+      <c r="C197" s="1">
+        <v>344840</v>
+      </c>
+    </row>
+    <row r="198" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B198" s="1">
+        <v>195</v>
+      </c>
+      <c r="C198" s="1">
+        <v>346630</v>
+      </c>
+    </row>
+    <row r="199" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B199" s="1">
+        <v>196</v>
+      </c>
+      <c r="C199" s="1">
+        <v>348420</v>
+      </c>
+    </row>
+    <row r="200" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B200" s="1">
+        <v>197</v>
+      </c>
+      <c r="C200" s="1">
+        <v>350210</v>
+      </c>
+    </row>
+    <row r="201" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B201" s="1">
+        <v>198</v>
+      </c>
+      <c r="C201" s="1">
+        <v>352000</v>
+      </c>
+    </row>
+    <row r="202" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B202" s="1">
+        <v>199</v>
+      </c>
+      <c r="C202" s="1">
+        <v>353790</v>
+      </c>
+    </row>
+    <row r="203" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B203" s="1">
+        <v>200</v>
+      </c>
+      <c r="C203" s="1">
+        <v>355580</v>
+      </c>
+    </row>
+    <row r="204" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B204" s="1">
+        <v>201</v>
+      </c>
+      <c r="C204" s="1">
+        <v>357370</v>
+      </c>
+    </row>
+    <row r="205" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B205" s="1">
+        <v>202</v>
+      </c>
+      <c r="C205" s="1">
+        <v>359160</v>
+      </c>
+    </row>
+    <row r="206" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B206" s="1">
+        <v>203</v>
+      </c>
+      <c r="C206" s="1">
+        <v>360950</v>
+      </c>
+    </row>
+    <row r="207" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B207" s="1">
+        <v>204</v>
+      </c>
+      <c r="C207" s="1">
+        <v>362740</v>
+      </c>
+    </row>
+    <row r="208" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B208" s="1">
+        <v>205</v>
+      </c>
+      <c r="C208" s="1">
+        <v>364530</v>
+      </c>
+    </row>
+    <row r="209" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B209" s="1">
+        <v>206</v>
+      </c>
+      <c r="C209" s="1">
+        <v>366320</v>
+      </c>
+    </row>
+    <row r="210" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B210" s="1">
+        <v>207</v>
+      </c>
+      <c r="C210" s="1">
+        <v>368110</v>
+      </c>
+    </row>
+    <row r="211" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B211" s="1">
+        <v>208</v>
+      </c>
+      <c r="C211" s="1">
+        <v>369900</v>
+      </c>
+    </row>
+    <row r="212" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B212" s="1">
+        <v>209</v>
+      </c>
+      <c r="C212" s="1">
+        <v>371690</v>
+      </c>
+    </row>
+    <row r="213" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B213" s="1">
+        <v>210</v>
+      </c>
+      <c r="C213" s="1">
+        <v>373480</v>
+      </c>
+    </row>
+    <row r="214" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B214" s="1">
+        <v>211</v>
+      </c>
+      <c r="C214" s="1">
+        <v>375270</v>
+      </c>
+    </row>
+    <row r="215" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B215" s="1">
+        <v>212</v>
+      </c>
+      <c r="C215" s="1">
+        <v>377060</v>
+      </c>
+    </row>
+    <row r="216" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B216" s="1">
+        <v>213</v>
+      </c>
+      <c r="C216" s="1">
+        <v>378850</v>
+      </c>
+    </row>
+    <row r="217" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B217" s="1">
+        <v>214</v>
+      </c>
+      <c r="C217" s="1">
+        <v>380640</v>
+      </c>
+    </row>
+    <row r="218" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B218" s="1">
+        <v>215</v>
+      </c>
+      <c r="C218" s="1">
+        <v>382430</v>
+      </c>
+    </row>
+    <row r="219" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B219" s="1">
+        <v>216</v>
+      </c>
+      <c r="C219" s="1">
+        <v>384220</v>
+      </c>
+    </row>
+    <row r="220" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B220" s="1">
+        <v>217</v>
+      </c>
+      <c r="C220" s="1">
+        <v>386010</v>
+      </c>
+    </row>
+    <row r="221" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B221" s="1">
+        <v>218</v>
+      </c>
+      <c r="C221" s="1">
+        <v>387800</v>
+      </c>
+    </row>
+    <row r="222" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B222" s="1">
+        <v>219</v>
+      </c>
+      <c r="C222" s="1">
+        <v>389590</v>
+      </c>
+    </row>
+    <row r="223" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B223" s="1">
+        <v>220</v>
+      </c>
+      <c r="C223" s="1">
+        <v>391380</v>
+      </c>
+    </row>
+    <row r="224" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B224" s="1">
+        <v>221</v>
+      </c>
+      <c r="C224" s="1">
+        <v>393170</v>
+      </c>
+    </row>
+    <row r="225" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B225" s="1">
+        <v>222</v>
+      </c>
+      <c r="C225" s="1">
+        <v>394960</v>
+      </c>
+    </row>
+    <row r="226" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B226" s="1">
+        <v>223</v>
+      </c>
+      <c r="C226" s="1">
+        <v>396750</v>
+      </c>
+    </row>
+    <row r="227" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B227" s="1">
+        <v>224</v>
+      </c>
+      <c r="C227" s="1">
+        <v>398540</v>
+      </c>
+    </row>
+    <row r="228" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B228" s="1">
+        <v>225</v>
+      </c>
+      <c r="C228" s="1">
+        <v>400330</v>
+      </c>
+    </row>
+    <row r="229" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B229" s="1">
+        <v>226</v>
+      </c>
+      <c r="C229" s="1">
+        <v>402120</v>
+      </c>
+    </row>
+    <row r="230" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B230" s="1">
+        <v>227</v>
+      </c>
+      <c r="C230" s="1">
+        <v>403910</v>
+      </c>
+    </row>
+    <row r="231" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B231" s="1">
+        <v>228</v>
+      </c>
+      <c r="C231" s="1">
+        <v>405700</v>
+      </c>
+    </row>
+    <row r="232" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B232" s="1">
+        <v>229</v>
+      </c>
+      <c r="C232" s="1">
+        <v>407490</v>
+      </c>
+    </row>
+    <row r="233" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B233" s="1">
+        <v>230</v>
+      </c>
+      <c r="C233" s="1">
+        <v>409280</v>
+      </c>
+    </row>
+    <row r="234" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B234" s="1">
+        <v>231</v>
+      </c>
+      <c r="C234" s="1">
+        <v>411070</v>
+      </c>
+    </row>
+    <row r="235" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B235" s="1">
+        <v>232</v>
+      </c>
+      <c r="C235" s="1">
+        <v>412860</v>
+      </c>
+    </row>
+    <row r="236" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B236" s="1">
+        <v>233</v>
+      </c>
+      <c r="C236" s="1">
+        <v>414650</v>
+      </c>
+    </row>
+    <row r="237" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B237" s="1">
+        <v>234</v>
+      </c>
+      <c r="C237" s="1">
+        <v>416440</v>
+      </c>
+    </row>
+    <row r="238" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B238" s="1">
+        <v>235</v>
+      </c>
+      <c r="C238" s="1">
+        <v>418230</v>
+      </c>
+    </row>
+    <row r="239" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B239" s="1">
+        <v>236</v>
+      </c>
+      <c r="C239" s="1">
+        <v>420020</v>
+      </c>
+    </row>
+    <row r="240" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B240" s="1">
+        <v>237</v>
+      </c>
+      <c r="C240" s="1">
+        <v>421810</v>
+      </c>
+    </row>
+    <row r="241" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B241" s="1">
+        <v>238</v>
+      </c>
+      <c r="C241" s="1">
+        <v>423600</v>
+      </c>
+    </row>
+    <row r="242" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B242" s="1">
+        <v>239</v>
+      </c>
+      <c r="C242" s="1">
+        <v>425390</v>
+      </c>
+    </row>
+    <row r="243" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B243" s="1">
+        <v>240</v>
+      </c>
+      <c r="C243" s="1">
+        <v>427180</v>
+      </c>
+    </row>
+    <row r="244" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B244" s="1">
+        <v>241</v>
+      </c>
+      <c r="C244" s="1">
+        <v>428970</v>
+      </c>
+    </row>
+    <row r="245" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B245" s="1">
+        <v>242</v>
+      </c>
+      <c r="C245" s="1">
+        <v>430760</v>
+      </c>
+    </row>
+    <row r="246" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B246" s="1">
+        <v>243</v>
+      </c>
+      <c r="C246" s="1">
+        <v>432550</v>
+      </c>
+    </row>
+    <row r="247" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B247" s="1">
+        <v>244</v>
+      </c>
+      <c r="C247" s="1">
+        <v>434340</v>
+      </c>
+    </row>
+    <row r="248" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B248" s="1">
+        <v>245</v>
+      </c>
+      <c r="C248" s="1">
+        <v>436130</v>
+      </c>
+    </row>
+    <row r="249" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B249" s="1">
+        <v>246</v>
+      </c>
+      <c r="C249" s="1">
+        <v>437920</v>
+      </c>
+    </row>
+    <row r="250" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B250" s="1">
+        <v>247</v>
+      </c>
+      <c r="C250" s="1">
+        <v>439710</v>
+      </c>
+    </row>
+    <row r="251" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B251" s="1">
+        <v>248</v>
+      </c>
+      <c r="C251" s="1">
+        <v>441500</v>
+      </c>
+    </row>
+    <row r="252" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B252" s="1">
+        <v>249</v>
+      </c>
+      <c r="C252" s="1">
+        <v>443290</v>
+      </c>
+    </row>
+    <row r="253" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B253" s="1">
+        <v>250</v>
+      </c>
+      <c r="C253" s="1">
+        <v>445080</v>
+      </c>
+    </row>
+    <row r="254" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B254" s="1">
+        <v>251</v>
+      </c>
+      <c r="C254" s="1">
+        <v>446870</v>
+      </c>
+    </row>
+    <row r="255" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B255" s="1">
+        <v>252</v>
+      </c>
+      <c r="C255" s="1">
+        <v>448660</v>
+      </c>
+    </row>
+    <row r="256" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B256" s="1">
+        <v>253</v>
+      </c>
+      <c r="C256" s="1">
+        <v>450450</v>
+      </c>
+    </row>
+    <row r="257" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B257" s="1">
+        <v>254</v>
+      </c>
+      <c r="C257" s="1">
+        <v>452240</v>
+      </c>
+    </row>
+    <row r="258" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B258" s="1">
+        <v>255</v>
+      </c>
+      <c r="C258" s="1">
+        <v>454030</v>
+      </c>
+    </row>
+    <row r="259" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B259" s="1">
+        <v>256</v>
+      </c>
+      <c r="C259" s="1">
+        <v>455820</v>
+      </c>
+    </row>
+    <row r="260" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B260" s="1">
+        <v>257</v>
+      </c>
+      <c r="C260" s="1">
+        <v>457610</v>
+      </c>
+    </row>
+    <row r="261" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B261" s="1">
+        <v>258</v>
+      </c>
+      <c r="C261" s="1">
+        <v>459400</v>
+      </c>
+    </row>
+    <row r="262" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B262" s="1">
+        <v>259</v>
+      </c>
+      <c r="C262" s="1">
+        <v>461190</v>
+      </c>
+    </row>
+    <row r="263" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B263" s="1">
+        <v>260</v>
+      </c>
+      <c r="C263" s="1">
+        <v>462980</v>
+      </c>
+    </row>
+    <row r="264" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B264" s="1">
+        <v>261</v>
+      </c>
+      <c r="C264" s="1">
+        <v>464770</v>
+      </c>
+    </row>
+    <row r="265" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B265" s="1">
+        <v>262</v>
+      </c>
+      <c r="C265" s="1">
+        <v>466560</v>
+      </c>
+    </row>
+    <row r="266" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B266" s="1">
+        <v>263</v>
+      </c>
+      <c r="C266" s="1">
+        <v>468350</v>
+      </c>
+    </row>
+    <row r="267" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B267" s="1">
+        <v>264</v>
+      </c>
+      <c r="C267" s="1">
+        <v>470140</v>
+      </c>
+    </row>
+    <row r="268" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B268" s="1">
+        <v>265</v>
+      </c>
+      <c r="C268" s="1">
+        <v>471930</v>
+      </c>
+    </row>
+    <row r="269" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B269" s="1">
+        <v>266</v>
+      </c>
+      <c r="C269" s="1">
+        <v>473720</v>
+      </c>
+    </row>
+    <row r="270" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B270" s="1">
+        <v>267</v>
+      </c>
+      <c r="C270" s="1">
+        <v>475510</v>
+      </c>
+    </row>
+    <row r="271" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B271" s="1">
+        <v>268</v>
+      </c>
+      <c r="C271" s="1">
+        <v>477300</v>
+      </c>
+    </row>
+    <row r="272" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B272" s="1">
+        <v>269</v>
+      </c>
+      <c r="C272" s="1">
+        <v>479090</v>
+      </c>
+    </row>
+    <row r="273" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B273" s="1">
+        <v>270</v>
+      </c>
+      <c r="C273" s="1">
+        <v>480880</v>
+      </c>
+    </row>
+    <row r="274" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B274" s="1">
+        <v>271</v>
+      </c>
+      <c r="C274" s="1">
+        <v>482670</v>
+      </c>
+    </row>
+    <row r="275" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B275" s="1">
+        <v>272</v>
+      </c>
+      <c r="C275" s="1">
+        <v>484460</v>
+      </c>
+    </row>
+    <row r="276" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B276" s="1">
+        <v>273</v>
+      </c>
+      <c r="C276" s="1">
+        <v>486250</v>
+      </c>
+    </row>
+    <row r="277" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B277" s="1">
+        <v>274</v>
+      </c>
+      <c r="C277" s="1">
+        <v>488040</v>
+      </c>
+    </row>
+    <row r="278" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B278" s="1">
+        <v>275</v>
+      </c>
+      <c r="C278" s="1">
+        <v>489830</v>
+      </c>
+    </row>
+    <row r="279" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B279" s="1">
+        <v>276</v>
+      </c>
+      <c r="C279" s="1">
+        <v>491620</v>
+      </c>
+    </row>
+    <row r="280" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B280" s="1">
+        <v>277</v>
+      </c>
+      <c r="C280" s="1">
+        <v>493410</v>
+      </c>
+    </row>
+    <row r="281" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B281" s="1">
+        <v>278</v>
+      </c>
+      <c r="C281" s="1">
+        <v>495200</v>
+      </c>
+    </row>
+    <row r="282" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B282" s="1">
+        <v>279</v>
+      </c>
+      <c r="C282" s="1">
+        <v>496990</v>
+      </c>
+    </row>
+    <row r="283" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B283" s="1">
+        <v>280</v>
+      </c>
+      <c r="C283" s="1">
+        <v>498780</v>
+      </c>
+    </row>
+    <row r="284" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B284" s="1">
+        <v>281</v>
+      </c>
+      <c r="C284" s="1">
+        <v>500570</v>
+      </c>
+    </row>
+    <row r="285" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B285" s="1">
+        <v>282</v>
+      </c>
+      <c r="C285" s="1">
+        <v>502360</v>
+      </c>
+    </row>
+    <row r="286" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B286" s="1">
+        <v>283</v>
+      </c>
+      <c r="C286" s="1">
+        <v>504150</v>
+      </c>
+    </row>
+    <row r="287" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B287" s="1">
+        <v>284</v>
+      </c>
+      <c r="C287" s="1">
+        <v>505940</v>
+      </c>
+    </row>
+    <row r="288" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B288" s="1">
+        <v>285</v>
+      </c>
+      <c r="C288" s="1">
+        <v>507730</v>
+      </c>
+    </row>
+    <row r="289" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B289" s="1">
+        <v>286</v>
+      </c>
+      <c r="C289" s="1">
+        <v>509520</v>
+      </c>
+    </row>
+    <row r="290" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B290" s="1">
+        <v>287</v>
+      </c>
+      <c r="C290" s="1">
+        <v>511310</v>
+      </c>
+    </row>
+    <row r="291" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B291" s="1">
+        <v>288</v>
+      </c>
+      <c r="C291" s="1">
+        <v>513100</v>
+      </c>
+    </row>
+    <row r="292" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B292" s="1">
+        <v>289</v>
+      </c>
+      <c r="C292" s="1">
+        <v>514890</v>
+      </c>
+    </row>
+    <row r="293" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B293" s="1">
+        <v>290</v>
+      </c>
+      <c r="C293" s="1">
+        <v>516680</v>
+      </c>
+    </row>
+    <row r="294" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B294" s="1">
+        <v>291</v>
+      </c>
+      <c r="C294" s="1">
+        <v>518470</v>
+      </c>
+    </row>
+    <row r="295" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B295" s="1">
+        <v>292</v>
+      </c>
+      <c r="C295" s="1">
+        <v>520260</v>
+      </c>
+    </row>
+    <row r="296" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B296" s="1">
+        <v>293</v>
+      </c>
+      <c r="C296" s="1">
+        <v>522050</v>
+      </c>
+    </row>
+    <row r="297" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B297" s="1">
+        <v>294</v>
+      </c>
+      <c r="C297" s="1">
+        <v>523840</v>
+      </c>
+    </row>
+    <row r="298" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B298" s="1">
+        <v>295</v>
+      </c>
+      <c r="C298" s="1">
+        <v>525630</v>
+      </c>
+    </row>
+    <row r="299" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B299" s="1">
+        <v>296</v>
+      </c>
+      <c r="C299" s="1">
+        <v>527420</v>
+      </c>
+    </row>
+    <row r="300" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B300" s="1">
+        <v>297</v>
+      </c>
+      <c r="C300" s="1">
+        <v>529210</v>
+      </c>
+    </row>
+    <row r="301" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B301" s="1">
+        <v>298</v>
+      </c>
+      <c r="C301" s="1">
+        <v>531000</v>
+      </c>
+    </row>
+    <row r="302" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B302" s="1">
+        <v>299</v>
+      </c>
+      <c r="C302" s="1">
+        <v>532790</v>
+      </c>
+    </row>
+    <row r="303" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B303" s="1">
+        <v>300</v>
+      </c>
+      <c r="C303" s="1">
+        <v>534580</v>
+      </c>
+    </row>
+    <row r="304" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B304" s="1">
+        <v>301</v>
+      </c>
+      <c r="C304" s="1">
+        <v>536370</v>
+      </c>
+    </row>
+    <row r="305" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B305" s="1">
+        <v>302</v>
+      </c>
+      <c r="C305" s="1">
+        <v>538160</v>
+      </c>
+    </row>
+    <row r="306" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B306" s="1">
+        <v>303</v>
+      </c>
+      <c r="C306" s="1">
+        <v>539950</v>
+      </c>
+    </row>
+    <row r="307" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B307" s="1">
+        <v>304</v>
+      </c>
+      <c r="C307" s="1">
+        <v>541740</v>
+      </c>
+    </row>
+    <row r="308" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B308" s="1">
+        <v>305</v>
+      </c>
+      <c r="C308" s="1">
+        <v>543530</v>
+      </c>
+    </row>
+    <row r="309" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B309" s="1">
+        <v>306</v>
+      </c>
+      <c r="C309" s="1">
+        <v>545320</v>
+      </c>
+    </row>
+    <row r="310" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B310" s="1">
+        <v>307</v>
+      </c>
+      <c r="C310" s="1">
+        <v>547110</v>
+      </c>
+    </row>
+    <row r="311" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B311" s="1">
+        <v>308</v>
+      </c>
+      <c r="C311" s="1">
+        <v>548900</v>
+      </c>
+    </row>
+    <row r="312" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B312" s="1">
+        <v>309</v>
+      </c>
+      <c r="C312" s="1">
+        <v>550690</v>
+      </c>
+    </row>
+    <row r="313" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B313" s="1">
+        <v>310</v>
+      </c>
+      <c r="C313" s="1">
+        <v>552480</v>
+      </c>
+    </row>
+    <row r="314" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B314" s="1">
+        <v>311</v>
+      </c>
+      <c r="C314" s="1">
+        <v>554270</v>
+      </c>
+    </row>
+    <row r="315" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B315" s="1">
+        <v>312</v>
+      </c>
+      <c r="C315" s="1">
+        <v>556060</v>
+      </c>
+    </row>
+    <row r="316" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B316" s="1">
+        <v>313</v>
+      </c>
+      <c r="C316" s="1">
+        <v>557850</v>
+      </c>
+    </row>
+    <row r="317" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B317" s="1">
+        <v>314</v>
+      </c>
+      <c r="C317" s="1">
+        <v>559640</v>
+      </c>
+    </row>
+    <row r="318" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B318" s="1">
+        <v>315</v>
+      </c>
+      <c r="C318" s="1">
+        <v>561430</v>
+      </c>
+    </row>
+    <row r="319" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B319" s="1">
+        <v>316</v>
+      </c>
+      <c r="C319" s="1">
+        <v>563220</v>
+      </c>
+    </row>
+    <row r="320" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B320" s="1">
+        <v>317</v>
+      </c>
+      <c r="C320" s="1">
+        <v>565010</v>
+      </c>
+    </row>
+    <row r="321" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B321" s="1">
+        <v>318</v>
+      </c>
+      <c r="C321" s="1">
+        <v>566800</v>
+      </c>
+    </row>
+    <row r="322" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B322" s="1">
+        <v>319</v>
+      </c>
+      <c r="C322" s="1">
+        <v>568590</v>
+      </c>
+    </row>
+    <row r="323" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B323" s="1">
+        <v>320</v>
+      </c>
+      <c r="C323" s="1">
+        <v>570380</v>
+      </c>
+    </row>
+    <row r="324" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B324" s="1">
+        <v>321</v>
+      </c>
+      <c r="C324" s="1">
+        <v>572170</v>
+      </c>
+    </row>
+    <row r="325" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B325" s="1">
+        <v>322</v>
+      </c>
+      <c r="C325" s="1">
+        <v>573960</v>
+      </c>
+    </row>
+    <row r="326" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B326" s="1">
+        <v>323</v>
+      </c>
+      <c r="C326" s="1">
+        <v>575750</v>
+      </c>
+    </row>
+    <row r="327" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B327" s="1">
+        <v>324</v>
+      </c>
+      <c r="C327" s="1">
+        <v>577540</v>
+      </c>
+    </row>
+    <row r="328" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B328" s="1">
+        <v>325</v>
+      </c>
+      <c r="C328" s="1">
+        <v>579330</v>
+      </c>
+    </row>
+    <row r="329" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B329" s="1">
+        <v>326</v>
+      </c>
+      <c r="C329" s="1">
+        <v>581120</v>
+      </c>
+    </row>
+    <row r="330" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B330" s="1">
+        <v>327</v>
+      </c>
+      <c r="C330" s="1">
+        <v>582910</v>
+      </c>
+    </row>
+    <row r="331" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B331" s="1">
+        <v>328</v>
+      </c>
+      <c r="C331" s="1">
+        <v>584700</v>
+      </c>
+    </row>
+    <row r="332" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B332" s="1">
+        <v>329</v>
+      </c>
+      <c r="C332" s="1">
+        <v>586490</v>
+      </c>
+    </row>
+    <row r="333" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B333" s="1">
+        <v>330</v>
+      </c>
+      <c r="C333" s="1">
+        <v>588280</v>
+      </c>
+    </row>
+    <row r="334" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B334" s="1">
+        <v>331</v>
+      </c>
+      <c r="C334" s="1">
+        <v>590070</v>
+      </c>
+    </row>
+    <row r="335" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B335" s="1">
+        <v>332</v>
+      </c>
+      <c r="C335" s="1">
+        <v>591860</v>
+      </c>
+    </row>
+    <row r="336" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B336" s="1">
+        <v>333</v>
+      </c>
+      <c r="C336" s="1">
+        <v>593650</v>
+      </c>
+    </row>
+    <row r="337" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B337" s="1">
+        <v>334</v>
+      </c>
+      <c r="C337" s="1">
+        <v>595440</v>
+      </c>
+    </row>
+    <row r="338" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B338" s="1">
+        <v>335</v>
+      </c>
+      <c r="C338" s="1">
+        <v>597230</v>
+      </c>
+    </row>
+    <row r="339" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B339" s="1">
+        <v>336</v>
+      </c>
+      <c r="C339" s="1">
+        <v>599020</v>
+      </c>
+    </row>
+    <row r="340" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B340" s="1">
+        <v>337</v>
+      </c>
+      <c r="C340" s="1">
+        <v>600810</v>
+      </c>
+    </row>
+    <row r="341" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B341" s="1">
+        <v>338</v>
+      </c>
+      <c r="C341" s="1">
+        <v>602600</v>
+      </c>
+    </row>
+    <row r="342" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B342" s="1">
+        <v>339</v>
+      </c>
+      <c r="C342" s="1">
+        <v>604390</v>
+      </c>
+    </row>
+    <row r="343" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B343" s="1">
+        <v>340</v>
+      </c>
+      <c r="C343" s="1">
+        <v>606180</v>
+      </c>
+    </row>
+    <row r="344" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B344" s="1">
+        <v>341</v>
+      </c>
+      <c r="C344" s="1">
+        <v>607970</v>
+      </c>
+    </row>
+    <row r="345" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B345" s="1">
+        <v>342</v>
+      </c>
+      <c r="C345" s="1">
+        <v>609760</v>
+      </c>
+    </row>
+    <row r="346" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B346" s="1">
+        <v>343</v>
+      </c>
+      <c r="C346" s="1">
+        <v>611550</v>
+      </c>
+    </row>
+    <row r="347" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B347" s="1">
+        <v>344</v>
+      </c>
+      <c r="C347" s="1">
+        <v>613340</v>
+      </c>
+    </row>
+    <row r="348" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B348" s="1">
+        <v>345</v>
+      </c>
+      <c r="C348" s="1">
+        <v>615130</v>
+      </c>
+    </row>
+    <row r="349" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B349" s="1">
+        <v>346</v>
+      </c>
+      <c r="C349" s="1">
+        <v>616920</v>
+      </c>
+    </row>
+    <row r="350" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B350" s="1">
+        <v>347</v>
+      </c>
+      <c r="C350" s="1">
+        <v>618710</v>
+      </c>
+    </row>
+    <row r="351" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B351" s="1">
+        <v>348</v>
+      </c>
+      <c r="C351" s="1">
+        <v>620500</v>
+      </c>
+    </row>
+    <row r="352" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B352" s="1">
+        <v>349</v>
+      </c>
+      <c r="C352" s="1">
+        <v>622290</v>
+      </c>
+    </row>
+    <row r="353" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B353" s="1">
+        <v>350</v>
+      </c>
+      <c r="C353" s="1">
+        <v>624080</v>
+      </c>
+    </row>
+    <row r="354" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B354" s="1">
+        <v>351</v>
+      </c>
+      <c r="C354" s="1">
+        <v>625870</v>
+      </c>
+    </row>
+    <row r="355" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B355" s="1">
+        <v>352</v>
+      </c>
+      <c r="C355" s="1">
+        <v>627660</v>
+      </c>
+    </row>
+    <row r="356" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B356" s="1">
+        <v>353</v>
+      </c>
+      <c r="C356" s="1">
+        <v>629450</v>
+      </c>
+    </row>
+    <row r="357" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B357" s="1">
+        <v>354</v>
+      </c>
+      <c r="C357" s="1">
+        <v>631240</v>
+      </c>
+    </row>
+    <row r="358" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B358" s="1">
+        <v>355</v>
+      </c>
+      <c r="C358" s="1">
+        <v>633030</v>
+      </c>
+    </row>
+    <row r="359" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B359" s="1">
+        <v>356</v>
+      </c>
+      <c r="C359" s="1">
+        <v>634820</v>
+      </c>
+    </row>
+    <row r="360" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B360" s="1">
+        <v>357</v>
+      </c>
+      <c r="C360" s="1">
+        <v>636610</v>
+      </c>
+    </row>
+    <row r="361" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B361" s="1">
+        <v>358</v>
+      </c>
+      <c r="C361" s="1">
+        <v>638400</v>
+      </c>
+    </row>
+    <row r="362" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B362" s="1">
+        <v>359</v>
+      </c>
+      <c r="C362" s="1">
+        <v>640190</v>
+      </c>
+    </row>
+    <row r="363" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B363" s="1">
+        <v>360</v>
+      </c>
+      <c r="C363" s="1">
+        <v>641980</v>
+      </c>
+    </row>
+    <row r="364" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B364" s="1">
+        <v>361</v>
+      </c>
+      <c r="C364" s="1">
+        <v>643770</v>
+      </c>
+    </row>
+    <row r="365" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B365" s="1">
+        <v>362</v>
+      </c>
+      <c r="C365" s="1">
+        <v>645560</v>
+      </c>
+    </row>
+    <row r="366" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B366" s="1">
+        <v>363</v>
+      </c>
+      <c r="C366" s="1">
+        <v>647350</v>
+      </c>
+    </row>
+    <row r="367" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B367" s="1">
+        <v>364</v>
+      </c>
+      <c r="C367" s="1">
+        <v>649140</v>
+      </c>
+    </row>
+    <row r="368" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B368" s="1">
+        <v>365</v>
+      </c>
+      <c r="C368" s="1">
+        <v>650930</v>
+      </c>
+    </row>
+    <row r="369" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B369" s="1">
+        <v>366</v>
+      </c>
+      <c r="C369" s="1">
+        <v>652720</v>
+      </c>
+    </row>
+    <row r="370" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B370" s="1">
+        <v>367</v>
+      </c>
+      <c r="C370" s="1">
+        <v>654510</v>
+      </c>
+    </row>
+    <row r="371" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B371" s="1">
+        <v>368</v>
+      </c>
+      <c r="C371" s="1">
+        <v>656300</v>
+      </c>
+    </row>
+    <row r="372" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B372" s="1">
+        <v>369</v>
+      </c>
+      <c r="C372" s="1">
+        <v>658090</v>
+      </c>
+    </row>
+    <row r="373" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B373" s="1">
+        <v>370</v>
+      </c>
+      <c r="C373" s="1">
+        <v>659880</v>
+      </c>
+    </row>
+    <row r="374" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B374" s="1">
+        <v>371</v>
+      </c>
+      <c r="C374" s="1">
+        <v>661670</v>
+      </c>
+    </row>
+    <row r="375" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B375" s="1">
+        <v>372</v>
+      </c>
+      <c r="C375" s="1">
+        <v>663460</v>
+      </c>
+    </row>
+    <row r="376" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B376" s="1">
+        <v>373</v>
+      </c>
+      <c r="C376" s="1">
+        <v>665250</v>
+      </c>
+    </row>
+    <row r="377" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B377" s="1">
+        <v>374</v>
+      </c>
+      <c r="C377" s="1">
+        <v>667040</v>
+      </c>
+    </row>
+    <row r="378" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B378" s="1">
+        <v>375</v>
+      </c>
+      <c r="C378" s="1">
+        <v>668830</v>
+      </c>
+    </row>
+    <row r="379" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B379" s="1">
+        <v>376</v>
+      </c>
+      <c r="C379" s="1">
+        <v>670620</v>
+      </c>
+    </row>
+    <row r="380" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B380" s="1">
+        <v>377</v>
+      </c>
+      <c r="C380" s="1">
+        <v>672410</v>
+      </c>
+    </row>
+    <row r="381" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B381" s="1">
+        <v>378</v>
+      </c>
+      <c r="C381" s="1">
+        <v>674200</v>
+      </c>
+    </row>
+    <row r="382" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B382" s="1">
+        <v>379</v>
+      </c>
+      <c r="C382" s="1">
+        <v>675990</v>
+      </c>
+    </row>
+    <row r="383" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B383" s="1">
+        <v>380</v>
+      </c>
+      <c r="C383" s="1">
+        <v>677780</v>
+      </c>
+    </row>
+    <row r="384" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B384" s="1">
+        <v>381</v>
+      </c>
+      <c r="C384" s="1">
+        <v>679570</v>
+      </c>
+    </row>
+    <row r="385" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B385" s="1">
+        <v>382</v>
+      </c>
+      <c r="C385" s="1">
+        <v>681360</v>
+      </c>
+    </row>
+    <row r="386" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B386" s="1">
+        <v>383</v>
+      </c>
+      <c r="C386" s="1">
+        <v>683150</v>
+      </c>
+    </row>
+    <row r="387" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B387" s="1">
+        <v>384</v>
+      </c>
+      <c r="C387" s="1">
+        <v>684940</v>
+      </c>
+    </row>
+    <row r="388" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B388" s="1">
+        <v>385</v>
+      </c>
+      <c r="C388" s="1">
+        <v>686730</v>
+      </c>
+    </row>
+    <row r="389" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B389" s="1">
+        <v>386</v>
+      </c>
+      <c r="C389" s="1">
+        <v>688520</v>
+      </c>
+    </row>
+    <row r="390" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B390" s="1">
+        <v>387</v>
+      </c>
+      <c r="C390" s="1">
+        <v>690310</v>
+      </c>
+    </row>
+    <row r="391" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B391" s="1">
+        <v>388</v>
+      </c>
+      <c r="C391" s="1">
+        <v>692100</v>
+      </c>
+    </row>
+    <row r="392" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B392" s="1">
+        <v>389</v>
+      </c>
+      <c r="C392" s="1">
+        <v>693890</v>
+      </c>
+    </row>
+    <row r="393" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B393" s="1">
+        <v>390</v>
+      </c>
+      <c r="C393" s="1">
+        <v>695680</v>
+      </c>
+    </row>
+    <row r="394" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B394" s="1">
+        <v>391</v>
+      </c>
+      <c r="C394" s="1">
+        <v>697470</v>
+      </c>
+    </row>
+    <row r="395" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B395" s="1">
+        <v>392</v>
+      </c>
+      <c r="C395" s="1">
+        <v>699260</v>
+      </c>
+    </row>
+    <row r="396" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B396" s="1">
+        <v>393</v>
+      </c>
+      <c r="C396" s="1">
+        <v>701050</v>
+      </c>
+    </row>
+    <row r="397" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B397" s="1">
+        <v>394</v>
+      </c>
+      <c r="C397" s="1">
+        <v>702840</v>
+      </c>
+    </row>
+    <row r="398" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B398" s="1">
+        <v>395</v>
+      </c>
+      <c r="C398" s="1">
+        <v>704630</v>
+      </c>
+    </row>
+    <row r="399" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B399" s="1">
+        <v>396</v>
+      </c>
+      <c r="C399" s="1">
+        <v>706420</v>
+      </c>
+    </row>
+    <row r="400" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B400" s="1">
+        <v>397</v>
+      </c>
+      <c r="C400" s="1">
+        <v>708210</v>
+      </c>
+    </row>
+    <row r="401" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B401" s="1">
+        <v>398</v>
+      </c>
+      <c r="C401" s="1">
+        <v>710000</v>
+      </c>
+    </row>
+    <row r="402" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B402" s="1">
+        <v>399</v>
+      </c>
+      <c r="C402" s="1">
+        <v>711790</v>
+      </c>
+    </row>
+    <row r="403" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B403" s="1">
+        <v>400</v>
+      </c>
+      <c r="C403" s="1">
+        <v>713580</v>
+      </c>
+    </row>
+    <row r="404" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B404" s="1">
+        <v>401</v>
+      </c>
+      <c r="C404" s="1">
+        <v>715370</v>
+      </c>
+    </row>
+    <row r="405" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B405" s="1">
+        <v>402</v>
+      </c>
+      <c r="C405" s="1">
+        <v>717160</v>
+      </c>
+    </row>
+    <row r="406" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B406" s="1">
+        <v>403</v>
+      </c>
+      <c r="C406" s="1">
+        <v>718950</v>
+      </c>
+    </row>
+    <row r="407" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B407" s="1">
+        <v>404</v>
+      </c>
+      <c r="C407" s="1">
+        <v>720740</v>
+      </c>
+    </row>
+    <row r="408" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B408" s="1">
+        <v>405</v>
+      </c>
+      <c r="C408" s="1">
+        <v>722530</v>
+      </c>
+    </row>
+    <row r="409" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B409" s="1">
+        <v>406</v>
+      </c>
+      <c r="C409" s="1">
+        <v>724320</v>
+      </c>
+    </row>
+    <row r="410" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B410" s="1">
+        <v>407</v>
+      </c>
+      <c r="C410" s="1">
+        <v>726110</v>
+      </c>
+    </row>
+    <row r="411" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B411" s="1">
+        <v>408</v>
+      </c>
+      <c r="C411" s="1">
+        <v>727900</v>
+      </c>
+    </row>
+    <row r="412" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B412" s="1">
+        <v>409</v>
+      </c>
+      <c r="C412" s="1">
+        <v>729690</v>
+      </c>
+    </row>
+    <row r="413" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B413" s="1">
+        <v>410</v>
+      </c>
+      <c r="C413" s="1">
+        <v>731480</v>
+      </c>
+    </row>
+    <row r="414" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B414" s="1">
+        <v>411</v>
+      </c>
+      <c r="C414" s="1">
+        <v>733270</v>
+      </c>
+    </row>
+    <row r="415" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B415" s="1">
+        <v>412</v>
+      </c>
+      <c r="C415" s="1">
+        <v>735060</v>
+      </c>
+    </row>
+    <row r="416" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B416" s="1">
+        <v>413</v>
+      </c>
+      <c r="C416" s="1">
+        <v>736850</v>
+      </c>
+    </row>
+    <row r="417" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B417" s="1">
+        <v>414</v>
+      </c>
+      <c r="C417" s="1">
+        <v>738640</v>
+      </c>
+    </row>
+    <row r="418" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B418" s="1">
+        <v>415</v>
+      </c>
+      <c r="C418" s="1">
+        <v>740430</v>
+      </c>
+    </row>
+    <row r="419" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B419" s="1">
+        <v>416</v>
+      </c>
+      <c r="C419" s="1">
+        <v>742220</v>
+      </c>
+    </row>
+    <row r="420" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B420" s="1">
+        <v>417</v>
+      </c>
+      <c r="C420" s="1">
+        <v>744010</v>
+      </c>
+    </row>
+    <row r="421" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B421" s="1">
+        <v>418</v>
+      </c>
+      <c r="C421" s="1">
+        <v>745800</v>
+      </c>
+    </row>
+    <row r="422" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B422" s="1">
+        <v>419</v>
+      </c>
+      <c r="C422" s="1">
+        <v>747590</v>
+      </c>
+    </row>
+    <row r="423" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B423" s="1">
+        <v>420</v>
+      </c>
+      <c r="C423" s="1">
+        <v>749380</v>
+      </c>
+    </row>
+    <row r="424" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B424" s="1">
+        <v>421</v>
+      </c>
+      <c r="C424" s="1">
+        <v>751170</v>
+      </c>
+    </row>
+    <row r="425" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B425" s="1">
+        <v>422</v>
+      </c>
+      <c r="C425" s="1">
+        <v>752960</v>
+      </c>
+    </row>
+    <row r="426" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B426" s="1">
+        <v>423</v>
+      </c>
+      <c r="C426" s="1">
+        <v>754750</v>
+      </c>
+    </row>
+    <row r="427" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B427" s="1">
+        <v>424</v>
+      </c>
+      <c r="C427" s="1">
+        <v>756540</v>
+      </c>
+    </row>
+    <row r="428" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B428" s="1">
+        <v>425</v>
+      </c>
+      <c r="C428" s="1">
+        <v>758330</v>
+      </c>
+    </row>
+    <row r="429" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B429" s="1">
+        <v>426</v>
+      </c>
+      <c r="C429" s="1">
+        <v>760120</v>
+      </c>
+    </row>
+    <row r="430" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B430" s="1">
+        <v>427</v>
+      </c>
+      <c r="C430" s="1">
+        <v>761910</v>
+      </c>
+    </row>
+    <row r="431" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B431" s="1">
+        <v>428</v>
+      </c>
+      <c r="C431" s="1">
+        <v>763700</v>
+      </c>
+    </row>
+    <row r="432" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B432" s="1">
+        <v>429</v>
+      </c>
+      <c r="C432" s="1">
+        <v>765490</v>
+      </c>
+    </row>
+    <row r="433" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B433" s="1">
+        <v>430</v>
+      </c>
+      <c r="C433" s="1">
+        <v>767280</v>
+      </c>
+    </row>
+    <row r="434" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B434" s="1">
+        <v>431</v>
+      </c>
+      <c r="C434" s="1">
+        <v>769070</v>
+      </c>
+    </row>
+    <row r="435" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B435" s="1">
+        <v>432</v>
+      </c>
+      <c r="C435" s="1">
+        <v>770860</v>
+      </c>
+    </row>
+    <row r="436" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B436" s="1">
+        <v>433</v>
+      </c>
+      <c r="C436" s="1">
+        <v>772650</v>
+      </c>
+    </row>
+    <row r="437" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B437" s="1">
+        <v>434</v>
+      </c>
+      <c r="C437" s="1">
+        <v>774440</v>
+      </c>
+    </row>
+    <row r="438" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B438" s="1">
+        <v>435</v>
+      </c>
+      <c r="C438" s="1">
+        <v>776230</v>
+      </c>
+    </row>
+    <row r="439" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B439" s="1">
+        <v>436</v>
+      </c>
+      <c r="C439" s="1">
+        <v>778020</v>
+      </c>
+    </row>
+    <row r="440" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B440" s="1">
+        <v>437</v>
+      </c>
+      <c r="C440" s="1">
+        <v>779810</v>
+      </c>
+    </row>
+    <row r="441" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B441" s="1">
+        <v>438</v>
+      </c>
+      <c r="C441" s="1">
+        <v>781600</v>
+      </c>
+    </row>
+    <row r="442" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B442" s="1">
+        <v>439</v>
+      </c>
+      <c r="C442" s="1">
+        <v>783390</v>
+      </c>
+    </row>
+    <row r="443" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B443" s="1">
+        <v>440</v>
+      </c>
+      <c r="C443" s="1">
+        <v>785180</v>
+      </c>
+    </row>
+    <row r="444" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B444" s="1">
+        <v>441</v>
+      </c>
+      <c r="C444" s="1">
+        <v>786970</v>
+      </c>
+    </row>
+    <row r="445" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B445" s="1">
+        <v>442</v>
+      </c>
+      <c r="C445" s="1">
+        <v>788760</v>
+      </c>
+    </row>
+    <row r="446" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B446" s="1">
+        <v>443</v>
+      </c>
+      <c r="C446" s="1">
+        <v>790550</v>
+      </c>
+    </row>
+    <row r="447" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B447" s="1">
+        <v>444</v>
+      </c>
+      <c r="C447" s="1">
+        <v>792340</v>
+      </c>
+    </row>
+    <row r="448" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B448" s="1">
+        <v>445</v>
+      </c>
+      <c r="C448" s="1">
+        <v>794130</v>
+      </c>
+    </row>
+    <row r="449" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B449" s="1">
+        <v>446</v>
+      </c>
+      <c r="C449" s="1">
+        <v>795920</v>
+      </c>
+    </row>
+    <row r="450" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B450" s="1">
+        <v>447</v>
+      </c>
+      <c r="C450" s="1">
+        <v>797710</v>
+      </c>
+    </row>
+    <row r="451" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B451" s="1">
+        <v>448</v>
+      </c>
+      <c r="C451" s="1">
+        <v>799500</v>
+      </c>
+    </row>
+    <row r="452" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B452" s="1">
+        <v>449</v>
+      </c>
+      <c r="C452" s="1">
+        <v>801290</v>
+      </c>
+    </row>
+    <row r="453" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B453" s="1">
+        <v>450</v>
+      </c>
+      <c r="C453" s="1">
+        <v>803080</v>
+      </c>
+    </row>
+    <row r="454" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B454" s="1">
+        <v>451</v>
+      </c>
+      <c r="C454" s="1">
+        <v>804870</v>
+      </c>
+    </row>
+    <row r="455" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B455" s="1">
+        <v>452</v>
+      </c>
+      <c r="C455" s="1">
+        <v>806660</v>
+      </c>
+    </row>
+    <row r="456" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B456" s="1">
+        <v>453</v>
+      </c>
+      <c r="C456" s="1">
+        <v>808450</v>
+      </c>
+    </row>
+    <row r="457" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B457" s="1">
+        <v>454</v>
+      </c>
+      <c r="C457" s="1">
+        <v>810240</v>
+      </c>
+    </row>
+    <row r="458" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B458" s="1">
+        <v>455</v>
+      </c>
+      <c r="C458" s="1">
+        <v>812030</v>
+      </c>
+    </row>
+    <row r="459" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B459" s="1">
+        <v>456</v>
+      </c>
+      <c r="C459" s="1">
+        <v>813820</v>
+      </c>
+    </row>
+    <row r="460" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B460" s="1">
+        <v>457</v>
+      </c>
+      <c r="C460" s="1">
+        <v>815610</v>
+      </c>
+    </row>
+    <row r="461" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B461" s="1">
+        <v>458</v>
+      </c>
+      <c r="C461" s="1">
+        <v>817400</v>
+      </c>
+    </row>
+    <row r="462" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B462" s="1">
+        <v>459</v>
+      </c>
+      <c r="C462" s="1">
+        <v>819190</v>
+      </c>
+    </row>
+    <row r="463" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B463" s="1">
+        <v>460</v>
+      </c>
+      <c r="C463" s="1">
+        <v>820980</v>
+      </c>
+    </row>
+    <row r="464" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B464" s="1">
+        <v>461</v>
+      </c>
+      <c r="C464" s="1">
+        <v>822770</v>
+      </c>
+    </row>
+    <row r="465" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B465" s="1">
+        <v>462</v>
+      </c>
+      <c r="C465" s="1">
+        <v>824560</v>
+      </c>
+    </row>
+    <row r="466" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B466" s="1">
+        <v>463</v>
+      </c>
+      <c r="C466" s="1">
+        <v>826350</v>
+      </c>
+    </row>
+    <row r="467" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B467" s="1">
+        <v>464</v>
+      </c>
+      <c r="C467" s="1">
+        <v>828140</v>
+      </c>
+    </row>
+    <row r="468" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B468" s="1">
+        <v>465</v>
+      </c>
+      <c r="C468" s="1">
+        <v>829930</v>
+      </c>
+    </row>
+    <row r="469" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B469" s="1">
+        <v>466</v>
+      </c>
+      <c r="C469" s="1">
+        <v>831720</v>
+      </c>
+    </row>
+    <row r="470" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B470" s="1">
+        <v>467</v>
+      </c>
+      <c r="C470" s="1">
+        <v>833510</v>
+      </c>
+    </row>
+    <row r="471" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B471" s="1">
+        <v>468</v>
+      </c>
+      <c r="C471" s="1">
+        <v>835300</v>
+      </c>
+    </row>
+    <row r="472" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B472" s="1">
+        <v>469</v>
+      </c>
+      <c r="C472" s="1">
+        <v>837090</v>
+      </c>
+    </row>
+    <row r="473" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B473" s="1">
+        <v>470</v>
+      </c>
+      <c r="C473" s="1">
+        <v>838880</v>
+      </c>
+    </row>
+    <row r="474" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B474" s="1">
+        <v>471</v>
+      </c>
+      <c r="C474" s="1">
+        <v>840670</v>
+      </c>
+    </row>
+    <row r="475" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B475" s="1">
+        <v>472</v>
+      </c>
+      <c r="C475" s="1">
+        <v>842460</v>
+      </c>
+    </row>
+    <row r="476" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B476" s="1">
+        <v>473</v>
+      </c>
+      <c r="C476" s="1">
+        <v>844250</v>
+      </c>
+    </row>
+    <row r="477" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B477" s="1">
+        <v>474</v>
+      </c>
+      <c r="C477" s="1">
+        <v>846040</v>
+      </c>
+    </row>
+    <row r="478" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B478" s="1">
+        <v>475</v>
+      </c>
+      <c r="C478" s="1">
+        <v>847830</v>
+      </c>
+    </row>
+    <row r="479" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B479" s="1">
+        <v>476</v>
+      </c>
+      <c r="C479" s="1">
+        <v>849620</v>
+      </c>
+    </row>
+    <row r="480" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B480" s="1">
+        <v>477</v>
+      </c>
+      <c r="C480" s="1">
+        <v>851410</v>
+      </c>
+    </row>
+    <row r="481" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B481" s="1">
+        <v>478</v>
+      </c>
+      <c r="C481" s="1">
+        <v>853200</v>
+      </c>
+    </row>
+    <row r="482" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B482" s="1">
+        <v>479</v>
+      </c>
+      <c r="C482" s="1">
+        <v>854990</v>
+      </c>
+    </row>
+    <row r="483" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B483" s="1">
+        <v>480</v>
+      </c>
+      <c r="C483" s="1">
+        <v>856780</v>
+      </c>
+    </row>
+    <row r="484" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B484" s="1">
+        <v>481</v>
+      </c>
+      <c r="C484" s="1">
+        <v>858570</v>
+      </c>
+    </row>
+    <row r="485" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B485" s="1">
+        <v>482</v>
+      </c>
+      <c r="C485" s="1">
+        <v>860360</v>
+      </c>
+    </row>
+    <row r="486" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B486" s="1">
+        <v>483</v>
+      </c>
+      <c r="C486" s="1">
+        <v>862150</v>
+      </c>
+    </row>
+    <row r="487" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B487" s="1">
+        <v>484</v>
+      </c>
+      <c r="C487" s="1">
+        <v>863940</v>
+      </c>
+    </row>
+    <row r="488" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B488" s="1">
+        <v>485</v>
+      </c>
+      <c r="C488" s="1">
+        <v>865730</v>
+      </c>
+    </row>
+    <row r="489" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B489" s="1">
+        <v>486</v>
+      </c>
+      <c r="C489" s="1">
+        <v>867520</v>
+      </c>
+    </row>
+    <row r="490" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B490" s="1">
+        <v>487</v>
+      </c>
+      <c r="C490" s="1">
+        <v>869310</v>
+      </c>
+    </row>
+    <row r="491" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B491" s="1">
+        <v>488</v>
+      </c>
+      <c r="C491" s="1">
+        <v>871100</v>
+      </c>
+    </row>
+    <row r="492" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B492" s="1">
+        <v>489</v>
+      </c>
+      <c r="C492" s="1">
+        <v>872890</v>
+      </c>
+    </row>
+    <row r="493" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B493" s="1">
+        <v>490</v>
+      </c>
+      <c r="C493" s="1">
+        <v>874680</v>
+      </c>
+    </row>
+    <row r="494" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B494" s="1">
+        <v>491</v>
+      </c>
+      <c r="C494" s="1">
+        <v>876470</v>
+      </c>
+    </row>
+    <row r="495" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B495" s="1">
+        <v>492</v>
+      </c>
+      <c r="C495" s="1">
+        <v>878260</v>
+      </c>
+    </row>
+    <row r="496" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B496" s="1">
+        <v>493</v>
+      </c>
+      <c r="C496" s="1">
+        <v>880050</v>
+      </c>
+    </row>
+    <row r="497" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B497" s="1">
+        <v>494</v>
+      </c>
+      <c r="C497" s="1">
+        <v>881840</v>
+      </c>
+    </row>
+    <row r="498" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B498" s="1">
+        <v>495</v>
+      </c>
+      <c r="C498" s="1">
+        <v>883630</v>
+      </c>
+    </row>
+    <row r="499" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B499" s="1">
+        <v>496</v>
+      </c>
+      <c r="C499" s="1">
+        <v>885420</v>
+      </c>
+    </row>
+    <row r="500" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B500" s="1">
+        <v>497</v>
+      </c>
+      <c r="C500" s="1">
+        <v>887210</v>
+      </c>
+    </row>
+    <row r="501" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B501" s="1">
+        <v>498</v>
+      </c>
+      <c r="C501" s="1">
+        <v>889000</v>
+      </c>
+    </row>
+    <row r="502" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B502" s="1">
+        <v>499</v>
+      </c>
+      <c r="C502" s="1">
+        <v>890790</v>
+      </c>
+    </row>
+    <row r="503" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B503" s="1">
+        <v>500</v>
+      </c>
+      <c r="C503" s="1">
+        <v>892580</v>
+      </c>
+    </row>
+    <row r="504" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B504" s="1">
+        <v>501</v>
+      </c>
+      <c r="C504" s="1">
+        <v>894370</v>
+      </c>
+    </row>
+    <row r="505" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B505" s="1">
+        <v>502</v>
+      </c>
+      <c r="C505" s="1">
+        <v>896160</v>
+      </c>
+    </row>
+    <row r="506" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B506" s="1">
+        <v>503</v>
+      </c>
+      <c r="C506" s="1">
+        <v>897950</v>
+      </c>
+    </row>
+    <row r="507" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B507" s="1">
+        <v>504</v>
+      </c>
+      <c r="C507" s="1">
+        <v>899740</v>
+      </c>
+    </row>
+    <row r="508" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B508" s="1">
+        <v>505</v>
+      </c>
+      <c r="C508" s="1">
+        <v>901530</v>
+      </c>
+    </row>
+    <row r="509" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B509" s="1">
+        <v>506</v>
+      </c>
+      <c r="C509" s="1">
+        <v>903320</v>
+      </c>
+    </row>
+    <row r="510" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B510" s="1">
+        <v>507</v>
+      </c>
+      <c r="C510" s="1">
+        <v>905110</v>
+      </c>
+    </row>
+    <row r="511" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B511" s="1">
+        <v>508</v>
+      </c>
+      <c r="C511" s="1">
+        <v>906900</v>
+      </c>
+    </row>
+    <row r="512" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B512" s="1">
+        <v>509</v>
+      </c>
+      <c r="C512" s="1">
+        <v>908690</v>
+      </c>
+    </row>
+    <row r="513" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B513" s="1">
+        <v>510</v>
+      </c>
+      <c r="C513" s="1">
+        <v>910480</v>
+      </c>
+    </row>
+    <row r="514" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B514" s="1">
+        <v>511</v>
+      </c>
+      <c r="C514" s="1">
+        <v>912270</v>
+      </c>
+    </row>
+    <row r="515" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B515" s="1">
+        <v>512</v>
+      </c>
+      <c r="C515" s="1">
+        <v>914060</v>
+      </c>
+    </row>
+    <row r="516" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B516" s="1">
+        <v>513</v>
+      </c>
+      <c r="C516" s="1">
+        <v>915850</v>
+      </c>
+    </row>
+    <row r="517" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B517" s="1">
+        <v>514</v>
+      </c>
+      <c r="C517" s="1">
+        <v>917640</v>
+      </c>
+    </row>
+    <row r="518" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B518" s="1">
+        <v>515</v>
+      </c>
+      <c r="C518" s="1">
+        <v>919430</v>
+      </c>
+    </row>
+    <row r="519" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B519" s="1">
+        <v>516</v>
+      </c>
+      <c r="C519" s="1">
+        <v>921220</v>
+      </c>
+    </row>
+    <row r="520" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B520" s="1">
+        <v>517</v>
+      </c>
+      <c r="C520" s="1">
+        <v>923010</v>
+      </c>
+    </row>
+    <row r="521" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B521" s="1">
+        <v>518</v>
+      </c>
+      <c r="C521" s="1">
+        <v>924800</v>
+      </c>
+    </row>
+    <row r="522" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B522" s="1">
+        <v>519</v>
+      </c>
+      <c r="C522" s="1">
+        <v>926590</v>
+      </c>
+    </row>
+    <row r="523" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B523" s="1">
+        <v>520</v>
+      </c>
+      <c r="C523" s="1">
+        <v>928380</v>
+      </c>
+    </row>
+    <row r="524" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B524" s="1">
+        <v>521</v>
+      </c>
+      <c r="C524" s="1">
+        <v>930170</v>
+      </c>
+    </row>
+    <row r="525" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B525" s="1">
+        <v>522</v>
+      </c>
+      <c r="C525" s="1">
+        <v>931960</v>
+      </c>
+    </row>
+    <row r="526" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B526" s="1">
+        <v>523</v>
+      </c>
+      <c r="C526" s="1">
+        <v>933750</v>
+      </c>
+    </row>
+    <row r="527" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B527" s="1">
+        <v>524</v>
+      </c>
+      <c r="C527" s="1">
+        <v>935540</v>
+      </c>
+    </row>
+    <row r="528" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B528" s="1">
+        <v>525</v>
+      </c>
+      <c r="C528" s="1">
+        <v>937330</v>
+      </c>
+    </row>
+    <row r="529" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B529" s="1">
+        <v>526</v>
+      </c>
+      <c r="C529" s="1">
+        <v>939120</v>
+      </c>
+    </row>
+    <row r="530" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B530" s="1">
+        <v>527</v>
+      </c>
+      <c r="C530" s="1">
+        <v>940910</v>
+      </c>
+    </row>
+    <row r="531" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B531" s="1">
+        <v>528</v>
+      </c>
+      <c r="C531" s="1">
+        <v>942700</v>
+      </c>
+    </row>
+    <row r="532" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B532" s="1">
+        <v>529</v>
+      </c>
+      <c r="C532" s="1">
+        <v>944490</v>
+      </c>
+    </row>
+    <row r="533" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B533" s="1">
+        <v>530</v>
+      </c>
+      <c r="C533" s="1">
+        <v>946280</v>
+      </c>
+    </row>
+    <row r="534" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B534" s="1">
+        <v>531</v>
+      </c>
+      <c r="C534" s="1">
+        <v>948070</v>
+      </c>
+    </row>
+    <row r="535" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B535" s="1">
+        <v>532</v>
+      </c>
+      <c r="C535" s="1">
+        <v>949860</v>
+      </c>
+    </row>
+    <row r="536" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B536" s="1">
+        <v>533</v>
+      </c>
+      <c r="C536" s="1">
+        <v>951650</v>
+      </c>
+    </row>
+    <row r="537" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B537" s="1">
+        <v>534</v>
+      </c>
+      <c r="C537" s="1">
+        <v>953440</v>
+      </c>
+    </row>
+    <row r="538" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B538" s="1">
+        <v>535</v>
+      </c>
+      <c r="C538" s="1">
+        <v>955230</v>
+      </c>
+    </row>
+    <row r="539" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B539" s="1">
+        <v>536</v>
+      </c>
+      <c r="C539" s="1">
+        <v>957020</v>
+      </c>
+    </row>
+    <row r="540" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B540" s="1">
+        <v>537</v>
+      </c>
+      <c r="C540" s="1">
+        <v>958810</v>
+      </c>
+    </row>
+    <row r="541" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B541" s="1">
+        <v>538</v>
+      </c>
+      <c r="C541" s="1">
+        <v>960600</v>
+      </c>
+    </row>
+    <row r="542" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B542" s="1">
+        <v>539</v>
+      </c>
+      <c r="C542" s="1">
+        <v>962390</v>
+      </c>
+    </row>
+    <row r="543" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B543" s="1">
+        <v>540</v>
+      </c>
+      <c r="C543" s="1">
+        <v>964180</v>
+      </c>
+    </row>
+    <row r="544" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B544" s="1">
+        <v>541</v>
+      </c>
+      <c r="C544" s="1">
+        <v>965970</v>
+      </c>
+    </row>
+    <row r="545" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B545" s="1">
+        <v>542</v>
+      </c>
+      <c r="C545" s="1">
+        <v>967760</v>
+      </c>
+    </row>
+    <row r="546" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B546" s="1">
+        <v>543</v>
+      </c>
+      <c r="C546" s="1">
+        <v>969550</v>
+      </c>
+    </row>
+    <row r="547" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B547" s="1">
+        <v>544</v>
+      </c>
+      <c r="C547" s="1">
+        <v>971340</v>
+      </c>
+    </row>
+    <row r="548" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B548" s="1">
+        <v>545</v>
+      </c>
+      <c r="C548" s="1">
+        <v>973130</v>
+      </c>
+    </row>
+    <row r="549" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B549" s="1">
+        <v>546</v>
+      </c>
+      <c r="C549" s="1">
+        <v>974920</v>
+      </c>
+    </row>
+    <row r="550" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B550" s="1">
+        <v>547</v>
+      </c>
+      <c r="C550" s="1">
+        <v>976710</v>
+      </c>
+    </row>
+    <row r="551" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B551" s="1">
+        <v>548</v>
+      </c>
+      <c r="C551" s="1">
+        <v>978500</v>
+      </c>
+    </row>
+    <row r="552" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B552" s="1">
+        <v>549</v>
+      </c>
+      <c r="C552" s="1">
+        <v>980290</v>
+      </c>
+    </row>
+    <row r="553" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B553" s="1">
+        <v>550</v>
+      </c>
+      <c r="C553" s="1">
+        <v>982080</v>
+      </c>
+    </row>
+    <row r="554" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B554" s="1">
+        <v>551</v>
+      </c>
+      <c r="C554" s="1">
+        <v>983870</v>
+      </c>
+    </row>
+    <row r="555" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B555" s="1">
+        <v>552</v>
+      </c>
+      <c r="C555" s="1">
+        <v>985660</v>
+      </c>
+    </row>
+    <row r="556" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B556" s="1">
+        <v>553</v>
+      </c>
+      <c r="C556" s="1">
+        <v>987450</v>
+      </c>
+    </row>
+    <row r="557" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B557" s="1">
+        <v>554</v>
+      </c>
+      <c r="C557" s="1">
+        <v>989240</v>
+      </c>
+    </row>
+    <row r="558" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B558" s="1">
+        <v>555</v>
+      </c>
+      <c r="C558" s="1">
+        <v>991030</v>
+      </c>
+    </row>
+    <row r="559" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B559" s="1">
+        <v>556</v>
+      </c>
+      <c r="C559" s="1">
+        <v>992820</v>
+      </c>
+    </row>
+    <row r="560" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B560" s="1">
+        <v>557</v>
+      </c>
+      <c r="C560" s="1">
+        <v>994610</v>
+      </c>
+    </row>
+    <row r="561" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B561" s="1">
+        <v>558</v>
+      </c>
+      <c r="C561" s="1">
+        <v>996400</v>
+      </c>
+    </row>
+    <row r="562" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B562" s="1">
+        <v>559</v>
+      </c>
+      <c r="C562" s="1">
+        <v>998190</v>
+      </c>
+    </row>
+    <row r="563" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B563" s="1">
+        <v>560</v>
+      </c>
+      <c r="C563" s="1">
+        <v>999980</v>
+      </c>
+    </row>
+    <row r="564" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B564" s="1">
+        <v>561</v>
+      </c>
+      <c r="C564" s="1">
+        <v>1001770</v>
+      </c>
+    </row>
+    <row r="565" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B565" s="1">
+        <v>562</v>
+      </c>
+      <c r="C565" s="1">
+        <v>1003560</v>
+      </c>
+    </row>
+    <row r="566" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B566" s="1">
+        <v>563</v>
+      </c>
+      <c r="C566" s="1">
+        <v>1005350</v>
+      </c>
+    </row>
+    <row r="567" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B567" s="1">
+        <v>564</v>
+      </c>
+      <c r="C567" s="1">
+        <v>1007140</v>
+      </c>
+    </row>
+    <row r="568" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B568" s="1">
+        <v>565</v>
+      </c>
+      <c r="C568" s="1">
+        <v>1008930</v>
+      </c>
+    </row>
+    <row r="569" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B569" s="1">
+        <v>566</v>
+      </c>
+      <c r="C569" s="1">
+        <v>1010720</v>
+      </c>
+    </row>
+    <row r="570" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B570" s="1">
+        <v>567</v>
+      </c>
+      <c r="C570" s="1">
+        <v>1012510</v>
+      </c>
+    </row>
+    <row r="571" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B571" s="1">
+        <v>568</v>
+      </c>
+      <c r="C571" s="1">
+        <v>1014300</v>
+      </c>
+    </row>
+    <row r="572" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B572" s="1">
+        <v>569</v>
+      </c>
+      <c r="C572" s="1">
+        <v>1016090</v>
+      </c>
+    </row>
+    <row r="573" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B573" s="1">
+        <v>570</v>
+      </c>
+      <c r="C573" s="1">
+        <v>1017880</v>
+      </c>
+    </row>
+    <row r="574" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B574" s="1">
+        <v>571</v>
+      </c>
+      <c r="C574" s="1">
+        <v>1019670</v>
+      </c>
+    </row>
+    <row r="575" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B575" s="1">
+        <v>572</v>
+      </c>
+      <c r="C575" s="1">
+        <v>1021460</v>
+      </c>
+    </row>
+    <row r="576" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B576" s="1">
+        <v>573</v>
+      </c>
+      <c r="C576" s="1">
+        <v>1023250</v>
+      </c>
+    </row>
+    <row r="577" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B577" s="1">
+        <v>574</v>
+      </c>
+      <c r="C577" s="1">
+        <v>1025040</v>
+      </c>
+    </row>
+    <row r="578" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B578" s="1">
+        <v>575</v>
+      </c>
+      <c r="C578" s="1">
+        <v>1026830</v>
+      </c>
+    </row>
+    <row r="579" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B579" s="1">
+        <v>576</v>
+      </c>
+      <c r="C579" s="1">
+        <v>1028620</v>
+      </c>
+    </row>
+    <row r="580" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B580" s="1">
+        <v>577</v>
+      </c>
+      <c r="C580" s="1">
+        <v>1030410</v>
+      </c>
+    </row>
+    <row r="581" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B581" s="1">
+        <v>578</v>
+      </c>
+      <c r="C581" s="1">
+        <v>1032200</v>
+      </c>
+    </row>
+    <row r="582" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B582" s="1">
+        <v>579</v>
+      </c>
+      <c r="C582" s="1">
+        <v>1033990</v>
+      </c>
+    </row>
+    <row r="583" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B583" s="1">
+        <v>580</v>
+      </c>
+      <c r="C583" s="1">
+        <v>1035780</v>
+      </c>
+    </row>
+    <row r="584" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B584" s="1">
+        <v>581</v>
+      </c>
+      <c r="C584" s="1">
+        <v>1037570</v>
+      </c>
+    </row>
+    <row r="585" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B585" s="1">
+        <v>582</v>
+      </c>
+      <c r="C585" s="1">
+        <v>1039360</v>
+      </c>
+    </row>
+    <row r="586" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B586" s="1">
+        <v>583</v>
+      </c>
+      <c r="C586" s="1">
+        <v>1041150</v>
+      </c>
+    </row>
+    <row r="587" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B587" s="1">
+        <v>584</v>
+      </c>
+      <c r="C587" s="1">
+        <v>1042940</v>
+      </c>
+    </row>
+    <row r="588" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B588" s="1">
+        <v>585</v>
+      </c>
+      <c r="C588" s="1">
+        <v>1044730</v>
+      </c>
+    </row>
+    <row r="589" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B589" s="1">
+        <v>586</v>
+      </c>
+      <c r="C589" s="1">
+        <v>1046520</v>
+      </c>
+    </row>
+    <row r="590" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B590" s="1">
+        <v>587</v>
+      </c>
+      <c r="C590" s="1">
+        <v>1048310</v>
+      </c>
+    </row>
+    <row r="591" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B591" s="1">
+        <v>588</v>
+      </c>
+      <c r="C591" s="1">
+        <v>1050100</v>
+      </c>
+    </row>
+    <row r="592" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B592" s="1">
+        <v>589</v>
+      </c>
+      <c r="C592" s="1">
+        <v>1051890</v>
+      </c>
+    </row>
+    <row r="593" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B593" s="1">
+        <v>590</v>
+      </c>
+      <c r="C593" s="1">
+        <v>1053680</v>
+      </c>
+    </row>
+    <row r="594" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B594" s="1">
+        <v>591</v>
+      </c>
+      <c r="C594" s="1">
+        <v>1055470</v>
+      </c>
+    </row>
+    <row r="595" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B595" s="1">
+        <v>592</v>
+      </c>
+      <c r="C595" s="1">
+        <v>1057260</v>
+      </c>
+    </row>
+    <row r="596" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B596" s="1">
+        <v>593</v>
+      </c>
+      <c r="C596" s="1">
+        <v>1059050</v>
+      </c>
+    </row>
+    <row r="597" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B597" s="1">
+        <v>594</v>
+      </c>
+      <c r="C597" s="1">
+        <v>1060840</v>
+      </c>
+    </row>
+    <row r="598" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B598" s="1">
+        <v>595</v>
+      </c>
+      <c r="C598" s="1">
+        <v>1062630</v>
+      </c>
+    </row>
+    <row r="599" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B599" s="1">
+        <v>596</v>
+      </c>
+      <c r="C599" s="1">
+        <v>1064420</v>
+      </c>
+    </row>
+    <row r="600" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B600" s="1">
+        <v>597</v>
+      </c>
+      <c r="C600" s="1">
+        <v>1066210</v>
+      </c>
+    </row>
+    <row r="601" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B601" s="1">
+        <v>598</v>
+      </c>
+      <c r="C601" s="1">
+        <v>1068000</v>
+      </c>
+    </row>
+    <row r="602" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B602" s="1">
+        <v>599</v>
+      </c>
+      <c r="C602" s="1">
+        <v>1069790</v>
+      </c>
+    </row>
+    <row r="603" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B603" s="1">
+        <v>600</v>
+      </c>
+      <c r="C603" s="1">
+        <v>1071580</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683"/>
   </bookViews>
   <sheets>
     <sheet name="#CharacterStat" sheetId="14" r:id="rId1"/>
@@ -40,19 +40,19 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>TotalExperience</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -69,19 +69,19 @@
       </rPr>
       <t>Stat</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BaseValue</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!StatDetail</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StatDetail_Atk_Base</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StatDetail_AtkSpeed_Base</t>
@@ -103,7 +103,7 @@
   </si>
   <si>
     <t>StatDetailID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -119,11 +119,11 @@
       </rPr>
       <t>erLevel</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StatDetail_MoveSpeed_Base</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StatDetail_EvasionRate_Base</t>
@@ -133,19 +133,27 @@
   </si>
   <si>
     <t>CharacterLevelExp</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -274,48 +282,48 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -593,7 +601,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -674,7 +682,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -775,7 +783,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5649,7 +5657,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -682,7 +682,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -601,7 +601,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -668,7 +668,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -601,7 +601,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -668,7 +668,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="1">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -668,7 +668,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="1">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>
@@ -682,7 +682,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -601,7 +601,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -682,7 +682,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -601,7 +601,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -601,7 +601,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
